--- a/data/ct_scoop/ct_scoop_links_2026-06-09.xlsx
+++ b/data/ct_scoop/ct_scoop_links_2026-06-09.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,103 +440,148 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MILFORD SCOOP: Kaos Speakeasy - Steakhouse announces indefinte closure after 3 months</t>
+          <t>WETHERSFIELD SCOOP: Food Street coming soon to Silas Deane!</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/milford-scoop-kaos-speakeasy-steakhouse-announces-indefinte-closure-after-3-months</t>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/wethersfield-scoop-food-street-coming-soon-to-silas-deane</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CHESHIRE SCOOP: Update on The Shops at Stone Bridge! Here is what is open and what is coming soon!</t>
+          <t>SOUTHINGTON SCOOP: Cava Restaurant to debut Mamma Mia themed rooftop experience!</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/cheshire-scoop-update-on-the-shops-at-stone-bridge-here-is-what-is-open-and-what-is-coming-soon</t>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/southington-scoop-cava-restaurant-to-debut-mamma-mia-themed-rooftop-experience</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NORWALK SCOOP: MOTW Coffee &amp; Pastries opening on Saturday!</t>
+          <t>BRANFORD SCOOP: New in-patient medical facility planned for Branford</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-fairfield-county-posts/norwalk-scoop-motw-coffee-pastries-opening-on-saturday</t>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/branford-scoop-new-in-patient-medical-facility-planned-for-branford</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ELLINGTON SCOOP: Kloter's Ice Cream Barn voted Best Ice Cream Shop in Tolland County!</t>
+          <t>MILFORD SCOOP: Kaos Speakeasy - Steakhouse announces indefinte closure after 3 months</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-tolland-county-posts/ellington-scoop-kloters-ice-cream-barn-voted-best-ice-cream-shop-in-tolland-county</t>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/milford-scoop-kaos-speakeasy-steakhouse-announces-indefinte-closure-after-3-months</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ROCKY HILL SCOOP: Brew Lab Cafe sets opening date in Rocky Hill</t>
+          <t>CHESHIRE SCOOP: Update on The Shops at Stone Bridge! Here is what is open and what is coming soon!</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/rocky-hill-scoop-brew-lab-cafe-sets-opening-date-in-rocky-hill</t>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/cheshire-scoop-update-on-the-shops-at-stone-bridge-here-is-what-is-open-and-what-is-coming-soon</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MILFORD SCOOP: Plan B Burger Bar closing</t>
+          <t>NORWALK SCOOP: MOTW Coffee &amp; Pastries opening on Saturday!</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/milford-scoop-plan-b-burger-bar-closing</t>
+          <t>https://www.theconnecticutscoop.com/all-fairfield-county-posts/norwalk-scoop-motw-coffee-pastries-opening-on-saturday</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SPRINGFIELD SCOOP: O'Reilly Auto Parts eyeing new Springfield location</t>
+          <t>ELLINGTON SCOOP: Kloter's Ice Cream Barn voted Best Ice Cream Shop in Tolland County!</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>46180</v>
       </c>
       <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-tolland-county-posts/ellington-scoop-kloters-ice-cream-barn-voted-best-ice-cream-shop-in-tolland-county</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ROCKY HILL SCOOP: Brew Lab Cafe sets opening date in Rocky Hill</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46180</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/rocky-hill-scoop-brew-lab-cafe-sets-opening-date-in-rocky-hill</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MILFORD SCOOP: Plan B Burger Bar closing</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46180</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/milford-scoop-plan-b-burger-bar-closing</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SPRINGFIELD SCOOP: O'Reilly Auto Parts eyeing new Springfield location</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46180</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>https://www.theconnecticutscoop.com/all-mass-posts/springfield-scoop-oreilly-auto-parts-eyeing-new-springfield-location</t>
         </is>
